--- a/docs/03_tests/社員削除BBテスト.xlsx
+++ b/docs/03_tests/社員削除BBテスト.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\削除\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3980F7CE-6D34-4E4D-9C70-42C23BA0D919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1952886A-0357-4292-B881-92277EB1453E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{25457097-483F-45A0-A2E4-D0D97B745892}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{25457097-483F-45A0-A2E4-D0D97B745892}"/>
   </bookViews>
   <sheets>
     <sheet name="条件" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="59">
   <si>
     <t>条件</t>
     <rPh sb="0" eb="2">
@@ -424,6 +424,44 @@
   </si>
   <si>
     <t>2-2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>リロードする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>値を保持したまま、Confirm画面のまま</t>
+    <rPh sb="0" eb="1">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>2-3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>続行をクリック</t>
+    <rPh sb="0" eb="2">
+      <t>ゾッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3-3</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -912,6 +950,154 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>20510</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>17530</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>403579</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>45356</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72163CF6-9F52-8A66-40EF-041652E692FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3640010" y="5913959"/>
+          <a:ext cx="2369712" cy="1615326"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>235858</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>108858</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="矢印: 下 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8E6C9EC-F429-1C85-B5C2-C703F2A7337F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4517572" y="7565572"/>
+          <a:ext cx="489857" cy="934357"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>45357</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>154215</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>117929</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>169430</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBA8CF14-F829-67BD-893E-C2031ADE8D78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3002643" y="8545286"/>
+          <a:ext cx="3383643" cy="1829501"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -997,6 +1183,50 @@
         <a:xfrm>
           <a:off x="3648075" y="3835401"/>
           <a:ext cx="3409950" cy="1947553"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>50801</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>31751</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>420205</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>222251</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47DD8F32-2F92-FF25-BA85-4DA58F47AB9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3708401" y="5975351"/>
+          <a:ext cx="3011004" cy="1562100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1533,7 +1763,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FB6615B-4B77-42B5-9503-220F0C108CC2}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="9.83203125" style="5" customWidth="1"/>
@@ -1580,6 +1810,17 @@
         <v>36</v>
       </c>
     </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D7" s="4" t="s">
         <v>30</v>
@@ -1588,6 +1829,16 @@
     <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D16" s="4" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="D27" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="7:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="G35" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1599,7 +1850,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AC60AB6-8112-45DA-8BAA-EDA9A21889CA}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="4" customWidth="1"/>
@@ -1649,6 +1900,17 @@
         <v>43</v>
       </c>
     </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="E8" s="4" t="s">
         <v>38</v>
@@ -1657,6 +1919,11 @@
     <row r="17" spans="5:5" x14ac:dyDescent="0.55000000000000004">
       <c r="E17" s="4" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="5:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="E27" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
